--- a/R088.xlsx
+++ b/R088.xlsx
@@ -783,7 +783,7 @@
         <v>9</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
